--- a/backend/exports/引出列表_货柜信息表_0317185613.xlsx
+++ b/backend/exports/引出列表_货柜信息表_0317185613.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gihub\logix\backend\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EB5638-166B-486B-A0AA-6C62461167EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BF7063-EB57-4E00-81BB-E6A000FEA745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4365" yWindow="4305" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="列表数据" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="178">
   <si>
     <t>序号</t>
   </si>
@@ -252,6 +252,309 @@
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MH FRANCE</t>
+  </si>
+  <si>
+    <t>26DSF00050</t>
+  </si>
+  <si>
+    <t>TIIU6394462</t>
+  </si>
+  <si>
+    <t>XMNE40277800</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>FEN JIN FANG ZHOU</t>
+  </si>
+  <si>
+    <t>ZG13</t>
+  </si>
+  <si>
+    <t>厦门港</t>
+  </si>
+  <si>
+    <t>勒阿弗尔</t>
+  </si>
+  <si>
+    <t>宁波天图翼联物流科技有限公司</t>
+  </si>
+  <si>
+    <t>Paris Warehouse Group</t>
+  </si>
+  <si>
+    <t>2026-03-25 00:00:00</t>
+  </si>
+  <si>
+    <t>盐田,深圳</t>
+  </si>
+  <si>
+    <t>林凡迪</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-05-11 06:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-30 00:48:04</t>
+  </si>
+  <si>
+    <t>26DSF00048</t>
+  </si>
+  <si>
+    <t>TIIU5951286</t>
+  </si>
+  <si>
+    <t>XMNE69601000</t>
+  </si>
+  <si>
+    <t>AOSOM ITALY SRL</t>
+  </si>
+  <si>
+    <t>25DSI02203</t>
+  </si>
+  <si>
+    <t>HMMU6232153</t>
+  </si>
+  <si>
+    <t>NBOZGPT66800</t>
+  </si>
+  <si>
+    <t>ONE FRIENDSHIP</t>
+  </si>
+  <si>
+    <t>011W</t>
+  </si>
+  <si>
+    <t>热那亚</t>
+  </si>
+  <si>
+    <t>Milan Warehouse Group</t>
+  </si>
+  <si>
+    <t>2026-01-19 00:00:00</t>
+  </si>
+  <si>
+    <t>乍浦港,平湖,嘉兴,浙江</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>2026-03-21 22:00:00</t>
+  </si>
+  <si>
+    <t>25DSI02202</t>
+  </si>
+  <si>
+    <t>GAOU6195045</t>
+  </si>
+  <si>
+    <t>25DSI02201</t>
+  </si>
+  <si>
+    <t>HMMU6855127</t>
+  </si>
+  <si>
+    <t>25DSI02200</t>
+  </si>
+  <si>
+    <t>KOCU5129260</t>
+  </si>
+  <si>
+    <t>25DSI02199</t>
+  </si>
+  <si>
+    <t>HMMU6019657</t>
+  </si>
+  <si>
+    <t>MH HANDEL GMBH</t>
+  </si>
+  <si>
+    <t>25DSG2718</t>
+  </si>
+  <si>
+    <t>KOCU5158309</t>
+  </si>
+  <si>
+    <t>HDMUSHAZR2Q45800</t>
+  </si>
+  <si>
+    <t>HMM ROTTERDAM</t>
+  </si>
+  <si>
+    <t>0018W</t>
+  </si>
+  <si>
+    <t>上海</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>宁波外运国际货运代理有限公司</t>
+  </si>
+  <si>
+    <t>Vechta Warehouse</t>
+  </si>
+  <si>
+    <t>2026-01-12 00:00:00</t>
+  </si>
+  <si>
+    <t>崔怡轩</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2026-03-23 20:00:00</t>
+  </si>
+  <si>
+    <t>25DSG2443</t>
+  </si>
+  <si>
+    <t>HMMU4746390</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>25DSG2442</t>
+  </si>
+  <si>
+    <t>KOCU4533766</t>
+  </si>
+  <si>
+    <t>25DSG2441</t>
+  </si>
+  <si>
+    <t>HMMU6641402</t>
+  </si>
+  <si>
+    <t>25DSE10574</t>
+  </si>
+  <si>
+    <t>KOCU4076382</t>
+  </si>
+  <si>
+    <t>SZPE17059000</t>
+  </si>
+  <si>
+    <t>ONE TREASURE</t>
+  </si>
+  <si>
+    <t>0027W</t>
+  </si>
+  <si>
+    <t>盐田</t>
+  </si>
+  <si>
+    <t>2026-01-28 00:00:00</t>
+  </si>
+  <si>
+    <t>大铲湾,深圳</t>
+  </si>
+  <si>
+    <t>2026-03-22 13:05:00</t>
+  </si>
+  <si>
+    <t>25DSE10573</t>
+  </si>
+  <si>
+    <t>KOCU4485267</t>
+  </si>
+  <si>
+    <t>25DSE10572</t>
+  </si>
+  <si>
+    <t>KOCU4495835</t>
+  </si>
+  <si>
+    <t>25DSE10571</t>
+  </si>
+  <si>
+    <t>HMMU6764346</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>25DSG2699</t>
+  </si>
+  <si>
+    <t>TCNU5678064</t>
+  </si>
+  <si>
+    <t>TJN0831640</t>
+  </si>
+  <si>
+    <t>CMA CGM CORAL</t>
+  </si>
+  <si>
+    <t>0BYO3S</t>
+  </si>
+  <si>
+    <t>天津新港</t>
+  </si>
+  <si>
+    <t>2026-01-21 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-03-30 04:30:00</t>
+  </si>
+  <si>
+    <t>25DSG2698</t>
+  </si>
+  <si>
+    <t>CXDU1919549</t>
   </si>
 </sst>
 </file>
@@ -321,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -336,6 +639,135 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -692,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AO23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="10" width="16" customWidth="1"/>
@@ -1051,7 +1483,7 @@
       </c>
     </row>
     <row r="4" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="40" t="s">
         <v>67</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1158,7 +1590,7 @@
       </c>
     </row>
     <row r="5" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="40" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1265,7 +1697,7 @@
       </c>
     </row>
     <row r="6" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="40" t="s">
         <v>73</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1370,6 +1802,1950 @@
       <c r="AM6" s="8" t="s">
         <v>62</v>
       </c>
+    </row>
+    <row r="7" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="16">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="R7" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="S7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="U7" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="V7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="W7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="X7" s="18">
+        <v>774</v>
+      </c>
+      <c r="Y7" s="19">
+        <v>69.510000000000005</v>
+      </c>
+      <c r="Z7" s="20">
+        <v>10544</v>
+      </c>
+      <c r="AA7" s="19">
+        <v>29751.38</v>
+      </c>
+      <c r="AB7" s="19">
+        <v>1731.81</v>
+      </c>
+      <c r="AC7" s="19">
+        <v>25812.5</v>
+      </c>
+      <c r="AD7" s="19">
+        <v>27315.01</v>
+      </c>
+      <c r="AE7" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF7" s="19">
+        <v>1728</v>
+      </c>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM7" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN7" s="13"/>
+      <c r="AO7" s="13"/>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A8" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="12">
+        <v>46106</v>
+      </c>
+      <c r="S8" t="s">
+        <v>89</v>
+      </c>
+      <c r="T8" t="s">
+        <v>90</v>
+      </c>
+      <c r="U8" s="21">
+        <v>46035</v>
+      </c>
+      <c r="V8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" t="s">
+        <v>58</v>
+      </c>
+      <c r="X8">
+        <v>736</v>
+      </c>
+      <c r="Y8">
+        <v>57.42</v>
+      </c>
+      <c r="Z8" s="22">
+        <v>6116.6</v>
+      </c>
+      <c r="AA8" s="22">
+        <v>19042.78</v>
+      </c>
+      <c r="AB8" s="22">
+        <v>1730.51</v>
+      </c>
+      <c r="AC8" s="22">
+        <v>16521.11</v>
+      </c>
+      <c r="AD8" s="22">
+        <v>18022.509999999998</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF8" s="22">
+        <v>1728</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="12">
+        <v>46153.25</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM8" s="12">
+        <v>46111.033379629633</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="26">
+        <v>0</v>
+      </c>
+      <c r="N9" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="O9" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="R9" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="U9" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="V9" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="X9" s="28">
+        <v>328</v>
+      </c>
+      <c r="Y9" s="29">
+        <v>64.260000000000005</v>
+      </c>
+      <c r="Z9" s="30">
+        <v>7795.4</v>
+      </c>
+      <c r="AA9" s="29">
+        <v>22604.3</v>
+      </c>
+      <c r="AB9" s="29">
+        <v>2277.0100000000002</v>
+      </c>
+      <c r="AC9" s="29">
+        <v>19363.16</v>
+      </c>
+      <c r="AD9" s="29">
+        <v>21313.67</v>
+      </c>
+      <c r="AE9" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF9" s="29">
+        <v>2274</v>
+      </c>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="28">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="28">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL9" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM9" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN9" s="23"/>
+      <c r="AO9" s="23"/>
+    </row>
+    <row r="10" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="26">
+        <v>0</v>
+      </c>
+      <c r="N10" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="P10" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="R10" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="S10" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="T10" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="U10" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="V10" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="X10" s="28">
+        <v>190</v>
+      </c>
+      <c r="Y10" s="29">
+        <v>66.37</v>
+      </c>
+      <c r="Z10" s="30">
+        <v>9380.5</v>
+      </c>
+      <c r="AA10" s="29">
+        <v>26144.05</v>
+      </c>
+      <c r="AB10" s="29">
+        <v>2277.44</v>
+      </c>
+      <c r="AC10" s="29">
+        <v>22395.1</v>
+      </c>
+      <c r="AD10" s="29">
+        <v>24345.98</v>
+      </c>
+      <c r="AE10" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF10" s="29">
+        <v>2274</v>
+      </c>
+      <c r="AG10" s="23"/>
+      <c r="AH10" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="28">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="28">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL10" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM10" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN10" s="23"/>
+      <c r="AO10" s="23"/>
+    </row>
+    <row r="11" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="26">
+        <v>0</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="P11" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="S11" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="T11" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="U11" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="V11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="X11" s="28">
+        <v>627</v>
+      </c>
+      <c r="Y11" s="29">
+        <v>67.67</v>
+      </c>
+      <c r="Z11" s="30">
+        <v>9886</v>
+      </c>
+      <c r="AA11" s="29">
+        <v>21259.03</v>
+      </c>
+      <c r="AB11" s="29">
+        <v>2276.85</v>
+      </c>
+      <c r="AC11" s="29">
+        <v>18210.47</v>
+      </c>
+      <c r="AD11" s="29">
+        <v>20160.86</v>
+      </c>
+      <c r="AE11" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF11" s="29">
+        <v>2274</v>
+      </c>
+      <c r="AG11" s="23"/>
+      <c r="AH11" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="28">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="28">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL11" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM11" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN11" s="23"/>
+      <c r="AO11" s="23"/>
+    </row>
+    <row r="12" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="26">
+        <v>0</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="P12" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="R12" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="S12" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="T12" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="U12" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="V12" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W12" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="X12" s="28">
+        <v>481</v>
+      </c>
+      <c r="Y12" s="29">
+        <v>64.91</v>
+      </c>
+      <c r="Z12" s="30">
+        <v>8340.1</v>
+      </c>
+      <c r="AA12" s="29">
+        <v>18623.39</v>
+      </c>
+      <c r="AB12" s="29">
+        <v>2276.5300000000002</v>
+      </c>
+      <c r="AC12" s="29">
+        <v>15952.99</v>
+      </c>
+      <c r="AD12" s="29">
+        <v>17903.099999999999</v>
+      </c>
+      <c r="AE12" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF12" s="29">
+        <v>2274</v>
+      </c>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="28">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="28">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL12" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM12" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN12" s="23"/>
+      <c r="AO12" s="23"/>
+    </row>
+    <row r="13" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="26">
+        <v>0</v>
+      </c>
+      <c r="N13" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="P13" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="R13" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="S13" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="T13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="U13" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="V13" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W13" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="X13" s="28">
+        <v>746</v>
+      </c>
+      <c r="Y13" s="29">
+        <v>62.35</v>
+      </c>
+      <c r="Z13" s="30">
+        <v>11575.5</v>
+      </c>
+      <c r="AA13" s="29">
+        <v>42733.37</v>
+      </c>
+      <c r="AB13" s="29">
+        <v>2309.4499999999998</v>
+      </c>
+      <c r="AC13" s="29">
+        <v>36604.379999999997</v>
+      </c>
+      <c r="AD13" s="29">
+        <v>38582.71</v>
+      </c>
+      <c r="AE13" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF13" s="29">
+        <v>2304</v>
+      </c>
+      <c r="AG13" s="23"/>
+      <c r="AH13" s="28">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="28">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="28">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL13" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM13" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN13" s="23"/>
+      <c r="AO13" s="23"/>
+    </row>
+    <row r="14" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="34">
+        <v>0</v>
+      </c>
+      <c r="N14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="P14" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q14" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="R14" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="S14" s="31"/>
+      <c r="T14" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="V14" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W14" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="X14" s="36">
+        <v>520</v>
+      </c>
+      <c r="Y14" s="37">
+        <v>67.98</v>
+      </c>
+      <c r="Z14" s="38">
+        <v>9310</v>
+      </c>
+      <c r="AA14" s="37">
+        <v>19116.400000000001</v>
+      </c>
+      <c r="AB14" s="37">
+        <v>1900.54</v>
+      </c>
+      <c r="AC14" s="37">
+        <v>16367.3</v>
+      </c>
+      <c r="AD14" s="37">
+        <v>17994.52</v>
+      </c>
+      <c r="AE14" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF14" s="37">
+        <v>1898</v>
+      </c>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="36">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="36">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="36">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL14" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM14" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN14" s="31"/>
+      <c r="AO14" s="31"/>
+    </row>
+    <row r="15" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="34">
+        <v>0</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O15" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="P15" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q15" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="R15" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="S15" s="31"/>
+      <c r="T15" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="V15" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W15" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="X15" s="36">
+        <v>823</v>
+      </c>
+      <c r="Y15" s="37">
+        <v>63.97</v>
+      </c>
+      <c r="Z15" s="38">
+        <v>17460.84</v>
+      </c>
+      <c r="AA15" s="37">
+        <v>34992.239999999998</v>
+      </c>
+      <c r="AB15" s="37">
+        <v>1902.46</v>
+      </c>
+      <c r="AC15" s="37">
+        <v>29957.29</v>
+      </c>
+      <c r="AD15" s="37">
+        <v>31586.13</v>
+      </c>
+      <c r="AE15" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF15" s="37">
+        <v>1898</v>
+      </c>
+      <c r="AG15" s="31"/>
+      <c r="AH15" s="36">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="36">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="36">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL15" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM15" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN15" s="31"/>
+      <c r="AO15" s="31"/>
+    </row>
+    <row r="16" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="34">
+        <v>0</v>
+      </c>
+      <c r="N16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O16" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="P16" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q16" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="R16" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="S16" s="31"/>
+      <c r="T16" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="V16" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="X16" s="36">
+        <v>373</v>
+      </c>
+      <c r="Y16" s="37">
+        <v>62.41</v>
+      </c>
+      <c r="Z16" s="38">
+        <v>16639.599999999999</v>
+      </c>
+      <c r="AA16" s="37">
+        <v>21725.89</v>
+      </c>
+      <c r="AB16" s="37">
+        <v>1900.86</v>
+      </c>
+      <c r="AC16" s="37">
+        <v>18599.68</v>
+      </c>
+      <c r="AD16" s="37">
+        <v>20227.16</v>
+      </c>
+      <c r="AE16" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF16" s="37">
+        <v>1898</v>
+      </c>
+      <c r="AG16" s="31"/>
+      <c r="AH16" s="36">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="36">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="36">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL16" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM16" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN16" s="31"/>
+      <c r="AO16" s="31"/>
+    </row>
+    <row r="17" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="34">
+        <v>0</v>
+      </c>
+      <c r="N17" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O17" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q17" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="R17" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="S17" s="31"/>
+      <c r="T17" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="V17" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="X17" s="36">
+        <v>338</v>
+      </c>
+      <c r="Y17" s="37">
+        <v>68.06</v>
+      </c>
+      <c r="Z17" s="38">
+        <v>22100.400000000001</v>
+      </c>
+      <c r="AA17" s="37">
+        <v>28157.94</v>
+      </c>
+      <c r="AB17" s="37">
+        <v>1931.64</v>
+      </c>
+      <c r="AC17" s="37">
+        <v>24108.44</v>
+      </c>
+      <c r="AD17" s="37">
+        <v>25762.27</v>
+      </c>
+      <c r="AE17" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF17" s="37">
+        <v>1928</v>
+      </c>
+      <c r="AG17" s="31"/>
+      <c r="AH17" s="36">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="36">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="36">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL17" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM17" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN17" s="31"/>
+      <c r="AO17" s="31"/>
+    </row>
+    <row r="18" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="42">
+        <v>0</v>
+      </c>
+      <c r="N18" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O18" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="P18" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q18" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="R18" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="S18" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="T18" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="U18" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="V18" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W18" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="X18" s="44">
+        <v>1281</v>
+      </c>
+      <c r="Y18" s="45">
+        <v>65.66</v>
+      </c>
+      <c r="Z18" s="46">
+        <v>7503</v>
+      </c>
+      <c r="AA18" s="45">
+        <v>31941.4</v>
+      </c>
+      <c r="AB18" s="45">
+        <v>1902.09</v>
+      </c>
+      <c r="AC18" s="45">
+        <v>23837.07</v>
+      </c>
+      <c r="AD18" s="45">
+        <v>25256.7</v>
+      </c>
+      <c r="AE18" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF18" s="45">
+        <v>1898</v>
+      </c>
+      <c r="AG18" s="39"/>
+      <c r="AH18" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL18" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM18" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN18" s="39"/>
+      <c r="AO18" s="39"/>
+    </row>
+    <row r="19" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J19" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="42">
+        <v>0</v>
+      </c>
+      <c r="N19" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O19" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="P19" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q19" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="R19" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="S19" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="T19" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="U19" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="V19" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W19" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="X19" s="44">
+        <v>542</v>
+      </c>
+      <c r="Y19" s="45">
+        <v>66.989999999999995</v>
+      </c>
+      <c r="Z19" s="46">
+        <v>4274.3</v>
+      </c>
+      <c r="AA19" s="45">
+        <v>12490.92</v>
+      </c>
+      <c r="AB19" s="45">
+        <v>1899.74</v>
+      </c>
+      <c r="AC19" s="45">
+        <v>9322.74</v>
+      </c>
+      <c r="AD19" s="45">
+        <v>10740.62</v>
+      </c>
+      <c r="AE19" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF19" s="45">
+        <v>1898</v>
+      </c>
+      <c r="AG19" s="39"/>
+      <c r="AH19" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL19" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM19" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN19" s="39"/>
+      <c r="AO19" s="39"/>
+    </row>
+    <row r="20" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="42">
+        <v>0</v>
+      </c>
+      <c r="N20" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O20" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="P20" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="R20" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="S20" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="T20" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="U20" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="V20" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W20" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="X20" s="44">
+        <v>593</v>
+      </c>
+      <c r="Y20" s="45">
+        <v>66.44</v>
+      </c>
+      <c r="Z20" s="46">
+        <v>8428.9</v>
+      </c>
+      <c r="AA20" s="45">
+        <v>37839.199999999997</v>
+      </c>
+      <c r="AB20" s="45">
+        <v>1902.81</v>
+      </c>
+      <c r="AC20" s="45">
+        <v>28241.11</v>
+      </c>
+      <c r="AD20" s="45">
+        <v>29661.279999999999</v>
+      </c>
+      <c r="AE20" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF20" s="45">
+        <v>1898</v>
+      </c>
+      <c r="AG20" s="39"/>
+      <c r="AH20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL20" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM20" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN20" s="39"/>
+      <c r="AO20" s="39"/>
+    </row>
+    <row r="21" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="42">
+        <v>0</v>
+      </c>
+      <c r="N21" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O21" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="P21" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q21" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="R21" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="S21" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="T21" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="U21" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="V21" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W21" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="X21" s="44">
+        <v>418</v>
+      </c>
+      <c r="Y21" s="45">
+        <v>65.430000000000007</v>
+      </c>
+      <c r="Z21" s="46">
+        <v>3854.9</v>
+      </c>
+      <c r="AA21" s="45">
+        <v>11561.7</v>
+      </c>
+      <c r="AB21" s="45">
+        <v>1929.63</v>
+      </c>
+      <c r="AC21" s="45">
+        <v>8630.01</v>
+      </c>
+      <c r="AD21" s="45">
+        <v>10070.19</v>
+      </c>
+      <c r="AE21" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF21" s="45">
+        <v>1928</v>
+      </c>
+      <c r="AG21" s="39"/>
+      <c r="AH21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL21" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM21" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN21" s="39"/>
+      <c r="AO21" s="39"/>
+    </row>
+    <row r="22" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="I22" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="J22" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="50">
+        <v>0</v>
+      </c>
+      <c r="N22" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="P22" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q22" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="R22" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="S22" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="T22" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="U22" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="V22" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="W22" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="X22" s="52">
+        <v>669</v>
+      </c>
+      <c r="Y22" s="53">
+        <v>67.16</v>
+      </c>
+      <c r="Z22" s="54">
+        <v>8981.5</v>
+      </c>
+      <c r="AA22" s="53">
+        <v>18003.29</v>
+      </c>
+      <c r="AB22" s="53">
+        <v>1820.4</v>
+      </c>
+      <c r="AC22" s="53">
+        <v>15491.91</v>
+      </c>
+      <c r="AD22" s="53">
+        <v>17058.439999999999</v>
+      </c>
+      <c r="AE22" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF22" s="53">
+        <v>1818</v>
+      </c>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="52">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="52">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="52">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL22" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM22" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN22" s="47"/>
+      <c r="AO22" s="47"/>
+    </row>
+    <row r="23" spans="1:41" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="I23" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="47"/>
+      <c r="L23" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23" s="50">
+        <v>0</v>
+      </c>
+      <c r="N23" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="O23" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="P23" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q23" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="R23" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="S23" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="T23" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="U23" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="V23" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="W23" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="X23" s="52">
+        <v>679</v>
+      </c>
+      <c r="Y23" s="53">
+        <v>67.010000000000005</v>
+      </c>
+      <c r="Z23" s="54">
+        <v>10761.4</v>
+      </c>
+      <c r="AA23" s="53">
+        <v>23904.42</v>
+      </c>
+      <c r="AB23" s="53">
+        <v>1846.12</v>
+      </c>
+      <c r="AC23" s="53">
+        <v>20572.46</v>
+      </c>
+      <c r="AD23" s="53">
+        <v>22161.14</v>
+      </c>
+      <c r="AE23" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF23" s="53">
+        <v>1843</v>
+      </c>
+      <c r="AG23" s="47"/>
+      <c r="AH23" s="52">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="52">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="52">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL23" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM23" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN23" s="47"/>
+      <c r="AO23" s="47"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
